--- a/HumanEval/TB Authors.xlsx
+++ b/HumanEval/TB Authors.xlsx
@@ -4,7 +4,8 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="rudra.dhar@research.iiit.ac.in" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="adyanshkakran@gmail.com" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="rudra.dhar@research.iiit.ac.in" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="46">
   <si>
     <t>Timestamp</t>
   </si>
@@ -71,22 +72,31 @@
     <t>Model_D_Comment</t>
   </si>
   <si>
+    <t>Adyansh</t>
+  </si>
+  <si>
     <t>Rudra Dhar</t>
+  </si>
+  <si>
+    <t>Finetuning</t>
   </si>
   <si>
     <t>DRAFT</t>
   </si>
   <si>
+    <t>Prompting</t>
+  </si>
+  <si>
     <t>RAFG</t>
   </si>
   <si>
-    <t>Prompting</t>
+    <t>The original title is actually too small or generic to mean anything.</t>
   </si>
   <si>
-    <t>Finetuning</t>
+    <t>the title is vague</t>
   </si>
   <si>
-    <t>The original title is actually too small or generic to mean anything.</t>
+    <t>@mattmanning making up people is sad</t>
   </si>
   <si>
     <t>Though the generated ADR kind of makes sense, its written in a bad way, almost like hallucinating.</t>
@@ -96,6 +106,51 @@
   </si>
   <si>
     <t>Produces non-sence html instead of ADR</t>
+  </si>
+  <si>
+    <t>it took the title as the command 😭</t>
+  </si>
+  <si>
+    <t>Generation incomplete</t>
+  </si>
+  <si>
+    <t>Hallucinating</t>
+  </si>
+  <si>
+    <t>there is no decision</t>
+  </si>
+  <si>
+    <t>Didn't complete generation.</t>
+  </si>
+  <si>
+    <t>Didn't take the Decision.</t>
+  </si>
+  <si>
+    <t>Hallucinated a bit.</t>
+  </si>
+  <si>
+    <t>no decision</t>
+  </si>
+  <si>
+    <t>Generation didn't complete.</t>
+  </si>
+  <si>
+    <t>Incomplete generation</t>
+  </si>
+  <si>
+    <t>It's a really bad data! Title is probably not captured properly.</t>
+  </si>
+  <si>
+    <t>Idea is correct, but the generation is hallucinating.</t>
+  </si>
+  <si>
+    <t>Incomplete Generation</t>
+  </si>
+  <si>
+    <t>alex who</t>
+  </si>
+  <si>
+    <t>incomplete generation</t>
   </si>
 </sst>
 </file>
@@ -167,6 +222,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -447,7 +506,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>46222.172217025465</v>
+        <v>46237.90151462963</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>19</v>
@@ -456,8 +515,3108 @@
         <v>3849.0</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N2" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R2" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>46237.902834305554</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1353.0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R3" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>46237.90372259259</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4">
+        <v>3382.0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N4" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R4" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>46237.90481083334</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="4">
+        <v>4223.0</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N5" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R5" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>46237.90543737268</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3846.0</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N6" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R6" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>46237.906167928246</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="4">
+        <v>51.0</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N7" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R7" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>46237.907328009256</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1684.0</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>46237.90853486111</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2896.0</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R9" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>46237.9096111574</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="4">
+        <v>250.0</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>46237.91034965278</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2875.0</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R11" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>46237.9110550926</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="4">
+        <v>3325.0</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R12" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>46237.925493229166</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1610.0</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>46237.92597502314</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="4">
+        <v>844.0</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>46237.93662741898</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="4">
+        <v>3013.0</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>46237.93730505787</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="4">
+        <v>3159.0</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N16" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R16" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>46237.93907375</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="4">
+        <v>740.0</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R17" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>46237.94033936343</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="4">
+        <v>3596.0</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R18" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>46237.941739629634</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2804.0</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M19" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R19" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>46237.94263384259</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="4">
+        <v>3231.0</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M20" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>46237.94383600695</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="4">
+        <v>121.0</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R21" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <v>46237.94586731482</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3247.0</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <v>46237.94781737268</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="4">
+        <v>3926.0</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R23" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <v>46237.95429418981</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1069.0</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <v>46237.95576960648</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="4">
+        <v>560.0</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <v>46237.95758190972</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3056.0</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R26" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>46237.95899717593</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="4">
+        <v>3341.0</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R27" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>46237.96013150463</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="4">
+        <v>3508.0</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F28" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>46237.96396145833</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="4">
+        <v>1952.0</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>46237.96491210649</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="4">
+        <v>429.0</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F30" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>46237.96651601852</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="4">
+        <v>501.0</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>46237.96746697917</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="4">
+        <v>1275.0</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M32" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>46237.96944447917</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="4">
+        <v>4168.0</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F33" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R33" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>46237.97014508102</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="4">
+        <v>1482.0</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J34" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M34" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>46237.99224663194</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1876.0</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F35" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M35" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N35" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R35" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>46237.99273665509</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="4">
+        <v>1213.0</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F36" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M36" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N36" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R36" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>46237.99337837963</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="4">
+        <v>2016.0</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F37" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N37" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R37" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>46237.99400883102</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="4">
+        <v>3379.0</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M38" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="N38" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R38" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>46237.994517037034</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="4">
+        <v>3397.0</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F39" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J39" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N39" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R39" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>46237.99496386574</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="4">
+        <v>1985.0</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F40" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M40" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N40" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R40" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>46237.99550827546</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="4">
+        <v>949.0</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M41" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N41" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R41" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>46237.996130810185</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" s="4">
+        <v>3284.0</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M42" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>46237.997184074076</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="4">
+        <v>2889.0</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>46237.99814098379</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="4">
+        <v>709.0</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>46237.998667175925</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="4">
+        <v>3096.0</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>46237.99936909722</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="4">
+        <v>982.0</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M46" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N46" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R46" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>46238.000505289354</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="4">
+        <v>3344.0</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>46238.001392314814</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="4">
+        <v>1375.0</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I48" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M48" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N48" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>46238.00233445602</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="4">
+        <v>993.0</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M49" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>46238.00276456018</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="4">
+        <v>3812.0</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F50" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J50" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>46238.003434583334</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1614.0</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F51" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I51" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J51" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M51" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>46238.00404322917</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" s="4">
+        <v>855.0</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M52" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N52" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>46238.004888449075</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="4">
+        <v>4234.0</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F53" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J53" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>46238.00717652778</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="4">
+        <v>3286.0</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F54" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M54" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N54" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R54" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>46238.00823315972</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="4">
+        <v>3652.0</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F55" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J55" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M55" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N55" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R55" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>46238.013038819445</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" s="4">
+        <v>3824.0</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F56" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N56" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R56" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>46238.013499548615</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" s="4">
+        <v>2911.0</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F57" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M57" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N57" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R57" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>46238.013881122686</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" s="4">
+        <v>2062.0</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M58" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>46238.01580121528</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" s="4">
+        <v>3143.0</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N59" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R59" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>46238.02113542824</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" s="4">
+        <v>4075.0</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J60" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M60" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N60" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R60" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>46238.02242260417</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" s="4">
+        <v>4075.0</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I61" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <v>46238.02304233796</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" s="4">
+        <v>66.0</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I62" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M62" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N62" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R62" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <v>46238.02366741898</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="4">
+        <v>2544.0</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J63" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <v>46238.02491504629</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="4">
+        <v>3881.0</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F64" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J64" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M64" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>46238.02591829861</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" s="4">
+        <v>986.0</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F65" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I65" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M65" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>46222.172217025465</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="C2" s="4">
+        <v>3849.0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E2" s="3">
         <v>2.0</v>
       </c>
@@ -465,7 +3624,7 @@
         <v>4.0</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3">
         <v>2.0</v>
@@ -474,7 +3633,7 @@
         <v>4.0</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" s="3">
         <v>2.0</v>
@@ -483,7 +3642,7 @@
         <v>4.0</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="3">
         <v>2.0</v>
@@ -497,13 +3656,13 @@
         <v>46225.60102349537</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4">
         <v>1353.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3">
         <v>1.0</v>
@@ -512,10 +3671,10 @@
         <v>1.0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I3" s="3">
         <v>2.0</v>
@@ -524,10 +3683,10 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M3" s="3">
         <v>1.0</v>
@@ -536,10 +3695,10 @@
         <v>3.0</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q3" s="3">
         <v>1.0</v>
@@ -548,7 +3707,7 @@
         <v>3.0</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -556,13 +3715,13 @@
         <v>46225.624809444445</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4">
         <v>3382.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3">
         <v>2.0</v>
@@ -571,7 +3730,7 @@
         <v>3.0</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I4" s="3">
         <v>2.0</v>
@@ -580,10 +3739,10 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M4" s="3">
         <v>3.0</v>
@@ -592,7 +3751,7 @@
         <v>5.0</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q4" s="3">
         <v>3.0</v>
@@ -606,13 +3765,13 @@
         <v>46225.62852349537</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="4">
         <v>4223.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3">
         <v>2.0</v>
@@ -621,7 +3780,7 @@
         <v>4.0</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I5" s="3">
         <v>2.0</v>
@@ -630,10 +3789,10 @@
         <v>3.0</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M5" s="3">
         <v>1.0</v>
@@ -642,15 +3801,2134 @@
         <v>1.0</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R5" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>46230.09894773148</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Q5" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="R5" s="3">
+      <c r="C6" s="4">
+        <v>3846.0</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N6" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R6" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>46230.10650782408</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="4">
+        <v>51.0</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N7" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R7" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>46230.113922743054</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1684.0</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R8" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>46230.123343009254</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2896.0</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R9" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>46231.84139128472</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="4">
+        <v>250.0</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J10" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>46231.84536614583</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2875.0</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R11" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>46232.75054260417</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="4">
+        <v>3325.0</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R12" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>46232.75557686343</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1610.0</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>46232.76180821759</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="4">
+        <v>844.0</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>46232.76564729167</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="4">
+        <v>3013.0</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>46232.776407812504</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="4">
+        <v>3159.0</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N16" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R16" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>46232.78047136574</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="4">
+        <v>740.0</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N17" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R17" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>46232.78326053241</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="4">
+        <v>3596.0</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N18" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R18" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>46232.78644847222</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2804.0</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N19" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R19" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>46232.78936142361</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="4">
+        <v>3231.0</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>46232.79335375</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="4">
+        <v>121.0</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R21" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <v>46232.85918023148</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="4">
+        <v>3247.0</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <v>46232.86953215278</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="4">
+        <v>3926.0</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R23" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <v>46232.87688391204</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1069.0</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M24" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <v>46232.88261299768</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="4">
+        <v>560.0</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F25" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <v>46233.00159622685</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3056.0</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R26" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>46233.01361976852</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="4">
+        <v>3341.0</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R27" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>46234.068551226854</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="4">
+        <v>3508.0</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F28" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>46234.070875694444</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="4">
+        <v>1952.0</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>46234.07546523148</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="4">
+        <v>429.0</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F30" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M30" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>46234.087179236114</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="4">
+        <v>501.0</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F31" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>46234.0930824074</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="4">
+        <v>1275.0</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>46234.103163645836</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="4">
+        <v>4168.0</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F33" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R33" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>46238.82448619213</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="4">
+        <v>1482.0</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J34" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>46238.83467055556</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1876.0</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F35" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M35" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N35" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R35" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>46238.84257037037</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="4">
+        <v>1213.0</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F36" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M36" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N36" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R36" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>46238.84952280093</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="4">
+        <v>2016.0</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F37" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M37" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N37" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R37" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>46244.98406592592</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="4">
+        <v>3379.0</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F38" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N38" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="R38" s="3">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>46244.991957743056</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="4">
+        <v>3397.0</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F39" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J39" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N39" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R39" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>46244.999857013885</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="4">
+        <v>1985.0</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F40" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M40" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N40" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R40" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>46245.00216123843</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="4">
+        <v>949.0</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F41" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I41" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M41" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N41" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R41" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>46245.06479855324</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="4">
+        <v>3284.0</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I42" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M42" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>46245.06901409722</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C43" s="4">
+        <v>2889.0</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M43" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>46245.071389386576</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="4">
+        <v>709.0</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>46245.076771990745</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="4">
+        <v>3096.0</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M45" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>46245.08922303241</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="4">
+        <v>982.0</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M46" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N46" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R46" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>46245.094949074075</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="4">
+        <v>3344.0</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>46245.09878515046</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="4">
+        <v>1375.0</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F48" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I48" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M48" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N48" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R48" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>46245.10444263888</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C49" s="4">
+        <v>993.0</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M49" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R49" s="3">
         <v>5.0</v>
       </c>
     </row>

--- a/HumanEval/TB Authors.xlsx
+++ b/HumanEval/TB Authors.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="47">
   <si>
     <t>Timestamp</t>
   </si>
@@ -75,28 +75,31 @@
     <t>Adyansh</t>
   </si>
   <si>
-    <t>Rudra Dhar</t>
+    <t>Finetuning</t>
   </si>
   <si>
-    <t>Finetuning</t>
+    <t>Prompting</t>
   </si>
   <si>
     <t>DRAFT</t>
   </si>
   <si>
-    <t>Prompting</t>
-  </si>
-  <si>
     <t>RAFG</t>
   </si>
   <si>
-    <t>The original title is actually too small or generic to mean anything.</t>
+    <t>Rudra Dhar</t>
   </si>
   <si>
     <t>the title is vague</t>
   </si>
   <si>
     <t>@mattmanning making up people is sad</t>
+  </si>
+  <si>
+    <t>The original title is actually too small or generic to mean anything.</t>
+  </si>
+  <si>
+    <t>it took the title as the command 😭</t>
   </si>
   <si>
     <t>Though the generated ADR kind of makes sense, its written in a bad way, almost like hallucinating.</t>
@@ -106,9 +109,6 @@
   </si>
   <si>
     <t>Produces non-sence html instead of ADR</t>
-  </si>
-  <si>
-    <t>it took the title as the command 😭</t>
   </si>
   <si>
     <t>Generation incomplete</t>
@@ -151,6 +151,9 @@
   </si>
   <si>
     <t>incomplete generation</t>
+  </si>
+  <si>
+    <t>Ground truth ADR is bad!</t>
   </si>
 </sst>
 </file>
@@ -515,7 +518,7 @@
         <v>3849.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="3">
         <v>2.0</v>
@@ -524,7 +527,7 @@
         <v>1.0</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I2" s="3">
         <v>2.0</v>
@@ -542,7 +545,7 @@
         <v>2.0</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q2" s="3">
         <v>4.0</v>
@@ -562,7 +565,7 @@
         <v>1353.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3">
         <v>1.0</v>
@@ -571,7 +574,7 @@
         <v>3.0</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="3">
         <v>1.0</v>
@@ -580,7 +583,7 @@
         <v>4.0</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M3" s="3">
         <v>1.0</v>
@@ -598,7 +601,7 @@
         <v>1.0</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -612,7 +615,7 @@
         <v>3382.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3">
         <v>1.0</v>
@@ -621,7 +624,7 @@
         <v>1.0</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
@@ -633,7 +636,7 @@
         <v>3.0</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M4" s="3">
         <v>4.0</v>
@@ -642,7 +645,7 @@
         <v>3.0</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q4" s="3">
         <v>2.0</v>
@@ -662,7 +665,7 @@
         <v>4223.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3">
         <v>2.0</v>
@@ -680,7 +683,7 @@
         <v>3.0</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M5" s="3">
         <v>1.0</v>
@@ -689,10 +692,10 @@
         <v>1.0</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q5" s="3">
         <v>1.0</v>
@@ -721,7 +724,7 @@
         <v>3.0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I6" s="3">
         <v>2.0</v>
@@ -730,7 +733,7 @@
         <v>2.0</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M6" s="3">
         <v>1.0</v>
@@ -739,7 +742,7 @@
         <v>2.0</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q6" s="3">
         <v>3.0</v>
@@ -768,7 +771,7 @@
         <v>4.0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I7" s="3">
         <v>3.0</v>
@@ -777,7 +780,7 @@
         <v>4.0</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M7" s="3">
         <v>2.0</v>
@@ -786,7 +789,7 @@
         <v>2.0</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q7" s="3">
         <v>1.0</v>
@@ -806,7 +809,7 @@
         <v>1684.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="3">
         <v>2.0</v>
@@ -815,7 +818,7 @@
         <v>3.0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I8" s="3">
         <v>4.0</v>
@@ -833,7 +836,7 @@
         <v>4.0</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q8" s="3">
         <v>3.0</v>
@@ -853,7 +856,7 @@
         <v>2896.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" s="3">
         <v>2.0</v>
@@ -871,7 +874,7 @@
         <v>1.0</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M9" s="3">
         <v>5.0</v>
@@ -880,7 +883,7 @@
         <v>3.0</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q9" s="3">
         <v>4.0</v>
@@ -900,7 +903,7 @@
         <v>250.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E10" s="3">
         <v>2.0</v>
@@ -918,7 +921,7 @@
         <v>2.0</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M10" s="3">
         <v>2.0</v>
@@ -927,7 +930,7 @@
         <v>3.0</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q10" s="3">
         <v>3.0</v>
@@ -947,7 +950,7 @@
         <v>2875.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="3">
         <v>3.0</v>
@@ -956,7 +959,7 @@
         <v>5.0</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I11" s="3">
         <v>3.0</v>
@@ -965,7 +968,7 @@
         <v>2.0</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M11" s="3">
         <v>3.0</v>
@@ -1003,7 +1006,7 @@
         <v>4.0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I12" s="3">
         <v>2.0</v>
@@ -1012,7 +1015,7 @@
         <v>3.0</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M12" s="3">
         <v>2.0</v>
@@ -1021,7 +1024,7 @@
         <v>3.0</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q12" s="3">
         <v>2.0</v>
@@ -1041,7 +1044,7 @@
         <v>1610.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E13" s="3">
         <v>3.0</v>
@@ -1059,7 +1062,7 @@
         <v>1.0</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M13" s="3">
         <v>2.0</v>
@@ -1068,7 +1071,7 @@
         <v>3.0</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q13" s="3">
         <v>3.0</v>
@@ -1088,7 +1091,7 @@
         <v>844.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" s="3">
         <v>4.0</v>
@@ -1097,7 +1100,7 @@
         <v>3.0</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I14" s="3">
         <v>3.0</v>
@@ -1106,7 +1109,7 @@
         <v>2.0</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M14" s="3">
         <v>2.0</v>
@@ -1135,7 +1138,7 @@
         <v>3013.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E15" s="3">
         <v>1.0</v>
@@ -1144,7 +1147,7 @@
         <v>1.0</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I15" s="3">
         <v>1.0</v>
@@ -1153,7 +1156,7 @@
         <v>3.0</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M15" s="3">
         <v>1.0</v>
@@ -1182,7 +1185,7 @@
         <v>3159.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E16" s="3">
         <v>5.0</v>
@@ -1200,7 +1203,7 @@
         <v>3.0</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M16" s="3">
         <v>4.0</v>
@@ -1209,7 +1212,7 @@
         <v>3.0</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="3">
         <v>2.0</v>
@@ -1229,7 +1232,7 @@
         <v>740.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E17" s="3">
         <v>4.0</v>
@@ -1238,7 +1241,7 @@
         <v>3.0</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I17" s="3">
         <v>4.0</v>
@@ -1247,7 +1250,7 @@
         <v>3.0</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M17" s="3">
         <v>4.0</v>
@@ -1285,7 +1288,7 @@
         <v>4.0</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I18" s="3">
         <v>5.0</v>
@@ -1294,7 +1297,7 @@
         <v>3.0</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M18" s="3">
         <v>4.0</v>
@@ -1303,7 +1306,7 @@
         <v>4.0</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q18" s="3">
         <v>5.0</v>
@@ -1332,7 +1335,7 @@
         <v>4.0</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I19" s="3">
         <v>4.0</v>
@@ -1341,7 +1344,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M19" s="3">
         <v>4.0</v>
@@ -1350,7 +1353,7 @@
         <v>3.0</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q19" s="3">
         <v>3.0</v>
@@ -1370,7 +1373,7 @@
         <v>3231.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E20" s="3">
         <v>3.0</v>
@@ -1388,7 +1391,7 @@
         <v>2.0</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M20" s="3">
         <v>3.0</v>
@@ -1397,7 +1400,7 @@
         <v>2.0</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q20" s="3">
         <v>3.0</v>
@@ -1426,7 +1429,7 @@
         <v>2.0</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I21" s="3">
         <v>2.0</v>
@@ -1435,7 +1438,7 @@
         <v>2.0</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M21" s="3">
         <v>1.0</v>
@@ -1447,7 +1450,7 @@
         <v>34</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q21" s="3">
         <v>3.0</v>
@@ -1467,7 +1470,7 @@
         <v>3247.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E22" s="3">
         <v>2.0</v>
@@ -1485,7 +1488,7 @@
         <v>2.0</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M22" s="3">
         <v>3.0</v>
@@ -1494,7 +1497,7 @@
         <v>2.0</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q22" s="3">
         <v>2.0</v>
@@ -1523,7 +1526,7 @@
         <v>1.0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I23" s="3">
         <v>2.0</v>
@@ -1535,7 +1538,7 @@
         <v>34</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M23" s="3">
         <v>4.0</v>
@@ -1544,7 +1547,7 @@
         <v>3.0</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q23" s="3">
         <v>3.0</v>
@@ -1564,7 +1567,7 @@
         <v>1069.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E24" s="3">
         <v>4.0</v>
@@ -1582,7 +1585,7 @@
         <v>4.0</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M24" s="3">
         <v>2.0</v>
@@ -1591,7 +1594,7 @@
         <v>2.0</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q24" s="3">
         <v>1.0</v>
@@ -1611,7 +1614,7 @@
         <v>560.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" s="3">
         <v>2.0</v>
@@ -1629,7 +1632,7 @@
         <v>2.0</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M25" s="3">
         <v>2.0</v>
@@ -1638,7 +1641,7 @@
         <v>1.0</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q25" s="3">
         <v>2.0</v>
@@ -1667,7 +1670,7 @@
         <v>3.0</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I26" s="3">
         <v>4.0</v>
@@ -1676,7 +1679,7 @@
         <v>3.0</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M26" s="3">
         <v>5.0</v>
@@ -1685,7 +1688,7 @@
         <v>3.0</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q26" s="3">
         <v>4.0</v>
@@ -1705,7 +1708,7 @@
         <v>3341.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27" s="3">
         <v>3.0</v>
@@ -1714,7 +1717,7 @@
         <v>5.0</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I27" s="3">
         <v>2.0</v>
@@ -1723,7 +1726,7 @@
         <v>4.0</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M27" s="3">
         <v>2.0</v>
@@ -1752,7 +1755,7 @@
         <v>3508.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E28" s="3">
         <v>3.0</v>
@@ -1770,7 +1773,7 @@
         <v>4.0</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M28" s="3">
         <v>4.0</v>
@@ -1779,7 +1782,7 @@
         <v>2.0</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q28" s="3">
         <v>3.0</v>
@@ -1808,7 +1811,7 @@
         <v>3.0</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I29" s="3">
         <v>4.0</v>
@@ -1817,7 +1820,7 @@
         <v>4.0</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M29" s="3">
         <v>3.0</v>
@@ -1826,7 +1829,7 @@
         <v>5.0</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q29" s="3">
         <v>3.0</v>
@@ -1846,7 +1849,7 @@
         <v>429.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E30" s="3">
         <v>5.0</v>
@@ -1864,7 +1867,7 @@
         <v>5.0</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M30" s="3">
         <v>4.0</v>
@@ -1873,7 +1876,7 @@
         <v>4.0</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q30" s="3">
         <v>3.0</v>
@@ -1893,7 +1896,7 @@
         <v>501.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E31" s="3">
         <v>4.0</v>
@@ -1902,7 +1905,7 @@
         <v>3.0</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I31" s="3">
         <v>3.0</v>
@@ -1920,7 +1923,7 @@
         <v>4.0</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q31" s="3">
         <v>3.0</v>
@@ -1940,7 +1943,7 @@
         <v>1275.0</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E32" s="3">
         <v>1.0</v>
@@ -1952,7 +1955,7 @@
         <v>38</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I32" s="3">
         <v>4.0</v>
@@ -1970,7 +1973,7 @@
         <v>5.0</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q32" s="3">
         <v>4.0</v>
@@ -1999,7 +2002,7 @@
         <v>4.0</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I33" s="3">
         <v>4.0</v>
@@ -2008,7 +2011,7 @@
         <v>4.0</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M33" s="3">
         <v>2.0</v>
@@ -2017,7 +2020,7 @@
         <v>4.0</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q33" s="3">
         <v>2.0</v>
@@ -2037,7 +2040,7 @@
         <v>1482.0</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E34" s="3">
         <v>1.0</v>
@@ -2046,7 +2049,7 @@
         <v>1.0</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I34" s="3">
         <v>3.0</v>
@@ -2055,7 +2058,7 @@
         <v>2.0</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M34" s="3">
         <v>1.0</v>
@@ -2093,7 +2096,7 @@
         <v>2.0</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I35" s="3">
         <v>4.0</v>
@@ -2102,7 +2105,7 @@
         <v>3.0</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M35" s="3">
         <v>3.0</v>
@@ -2111,7 +2114,7 @@
         <v>2.0</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q35" s="3">
         <v>2.0</v>
@@ -2131,7 +2134,7 @@
         <v>1213.0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E36" s="3">
         <v>2.0</v>
@@ -2140,7 +2143,7 @@
         <v>2.0</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I36" s="3">
         <v>2.0</v>
@@ -2149,7 +2152,7 @@
         <v>2.0</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M36" s="3">
         <v>4.0</v>
@@ -2178,7 +2181,7 @@
         <v>2016.0</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E37" s="3">
         <v>2.0</v>
@@ -2187,7 +2190,7 @@
         <v>1.0</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I37" s="3">
         <v>3.0</v>
@@ -2196,7 +2199,7 @@
         <v>4.0</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M37" s="3">
         <v>4.0</v>
@@ -2225,7 +2228,7 @@
         <v>3379.0</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" s="3">
         <v>1.0</v>
@@ -2234,7 +2237,7 @@
         <v>1.0</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I38" s="3">
         <v>1.0</v>
@@ -2252,7 +2255,7 @@
         <v>5.0</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q38" s="3">
         <v>5.0</v>
@@ -2281,7 +2284,7 @@
         <v>4.0</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I39" s="3">
         <v>3.0</v>
@@ -2290,7 +2293,7 @@
         <v>3.0</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M39" s="3">
         <v>3.0</v>
@@ -2299,7 +2302,7 @@
         <v>2.0</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q39" s="3">
         <v>4.0</v>
@@ -2319,7 +2322,7 @@
         <v>1985.0</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E40" s="3">
         <v>3.0</v>
@@ -2328,7 +2331,7 @@
         <v>4.0</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I40" s="3">
         <v>2.0</v>
@@ -2346,7 +2349,7 @@
         <v>3.0</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q40" s="3">
         <v>4.0</v>
@@ -2366,7 +2369,7 @@
         <v>949.0</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E41" s="3">
         <v>2.0</v>
@@ -2375,7 +2378,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I41" s="3">
         <v>2.0</v>
@@ -2393,7 +2396,7 @@
         <v>4.0</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q41" s="3">
         <v>5.0</v>
@@ -2413,7 +2416,7 @@
         <v>3284.0</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E42" s="3">
         <v>4.0</v>
@@ -2422,7 +2425,7 @@
         <v>3.0</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I42" s="3">
         <v>4.0</v>
@@ -2440,7 +2443,7 @@
         <v>2.0</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q42" s="3">
         <v>4.0</v>
@@ -2460,7 +2463,7 @@
         <v>2889.0</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E43" s="3">
         <v>4.0</v>
@@ -2469,7 +2472,7 @@
         <v>2.0</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I43" s="3">
         <v>4.0</v>
@@ -2478,7 +2481,7 @@
         <v>3.0</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M43" s="3">
         <v>4.0</v>
@@ -2516,7 +2519,7 @@
         <v>1.0</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I44" s="3">
         <v>2.0</v>
@@ -2525,7 +2528,7 @@
         <v>2.0</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M44" s="3">
         <v>4.0</v>
@@ -2534,7 +2537,7 @@
         <v>4.0</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q44" s="3">
         <v>1.0</v>
@@ -2563,7 +2566,7 @@
         <v>5.0</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I45" s="3">
         <v>4.0</v>
@@ -2572,7 +2575,7 @@
         <v>2.0</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M45" s="3">
         <v>3.0</v>
@@ -2581,7 +2584,7 @@
         <v>2.0</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q45" s="3">
         <v>4.0</v>
@@ -2601,7 +2604,7 @@
         <v>982.0</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E46" s="3">
         <v>3.0</v>
@@ -2610,7 +2613,7 @@
         <v>5.0</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I46" s="3">
         <v>3.0</v>
@@ -2628,7 +2631,7 @@
         <v>4.0</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q46" s="3">
         <v>4.0</v>
@@ -2657,7 +2660,7 @@
         <v>3.0</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I47" s="3">
         <v>4.0</v>
@@ -2666,7 +2669,7 @@
         <v>4.0</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M47" s="3">
         <v>4.0</v>
@@ -2675,7 +2678,7 @@
         <v>2.0</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q47" s="3">
         <v>3.0</v>
@@ -2698,7 +2701,7 @@
         <v>1375.0</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E48" s="3">
         <v>3.0</v>
@@ -2716,7 +2719,7 @@
         <v>1.0</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M48" s="3">
         <v>4.0</v>
@@ -2725,7 +2728,7 @@
         <v>2.0</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q48" s="3">
         <v>2.0</v>
@@ -2745,7 +2748,7 @@
         <v>993.0</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E49" s="3">
         <v>2.0</v>
@@ -2754,7 +2757,7 @@
         <v>2.0</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I49" s="3">
         <v>2.0</v>
@@ -2772,7 +2775,7 @@
         <v>4.0</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q49" s="3">
         <v>2.0</v>
@@ -2792,7 +2795,7 @@
         <v>3812.0</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E50" s="3">
         <v>2.0</v>
@@ -2810,7 +2813,7 @@
         <v>5.0</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M50" s="3">
         <v>4.0</v>
@@ -2819,7 +2822,7 @@
         <v>4.0</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q50" s="3">
         <v>3.0</v>
@@ -2839,7 +2842,7 @@
         <v>1614.0</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E51" s="3">
         <v>4.0</v>
@@ -2848,7 +2851,7 @@
         <v>3.0</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I51" s="3">
         <v>1.0</v>
@@ -2866,7 +2869,7 @@
         <v>2.0</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q51" s="3">
         <v>4.0</v>
@@ -2886,7 +2889,7 @@
         <v>855.0</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E52" s="3">
         <v>2.0</v>
@@ -2895,7 +2898,7 @@
         <v>1.0</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I52" s="3">
         <v>4.0</v>
@@ -2904,7 +2907,7 @@
         <v>1.0</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M52" s="3">
         <v>3.0</v>
@@ -2933,7 +2936,7 @@
         <v>4234.0</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E53" s="3">
         <v>4.0</v>
@@ -2942,7 +2945,7 @@
         <v>2.0</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I53" s="3">
         <v>4.0</v>
@@ -2951,7 +2954,7 @@
         <v>3.0</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M53" s="3">
         <v>3.0</v>
@@ -2989,7 +2992,7 @@
         <v>2.0</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I54" s="3">
         <v>3.0</v>
@@ -2998,7 +3001,7 @@
         <v>2.0</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M54" s="3">
         <v>3.0</v>
@@ -3007,7 +3010,7 @@
         <v>3.0</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q54" s="3">
         <v>2.0</v>
@@ -3027,7 +3030,7 @@
         <v>3652.0</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E55" s="3">
         <v>4.0</v>
@@ -3036,7 +3039,7 @@
         <v>2.0</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I55" s="3">
         <v>4.0</v>
@@ -3045,7 +3048,7 @@
         <v>3.0</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M55" s="3">
         <v>4.0</v>
@@ -3074,7 +3077,7 @@
         <v>3824.0</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E56" s="3">
         <v>4.0</v>
@@ -3083,7 +3086,7 @@
         <v>2.0</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I56" s="3">
         <v>3.0</v>
@@ -3092,7 +3095,7 @@
         <v>2.0</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M56" s="3">
         <v>4.0</v>
@@ -3130,7 +3133,7 @@
         <v>3.0</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I57" s="3">
         <v>5.0</v>
@@ -3139,7 +3142,7 @@
         <v>4.0</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M57" s="3">
         <v>2.0</v>
@@ -3148,7 +3151,7 @@
         <v>2.0</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q57" s="3">
         <v>2.0</v>
@@ -3168,7 +3171,7 @@
         <v>2062.0</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E58" s="3">
         <v>5.0</v>
@@ -3177,7 +3180,7 @@
         <v>5.0</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I58" s="3">
         <v>4.0</v>
@@ -3195,7 +3198,7 @@
         <v>2.0</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q58" s="3">
         <v>4.0</v>
@@ -3215,7 +3218,7 @@
         <v>3143.0</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E59" s="3">
         <v>1.0</v>
@@ -3233,7 +3236,7 @@
         <v>2.0</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M59" s="3">
         <v>3.0</v>
@@ -3242,7 +3245,7 @@
         <v>2.0</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q59" s="3">
         <v>4.0</v>
@@ -3262,7 +3265,7 @@
         <v>4075.0</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E60" s="3">
         <v>2.0</v>
@@ -3271,7 +3274,7 @@
         <v>1.0</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I60" s="3">
         <v>3.0</v>
@@ -3280,7 +3283,7 @@
         <v>2.0</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M60" s="3">
         <v>2.0</v>
@@ -3309,7 +3312,7 @@
         <v>4075.0</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E61" s="3">
         <v>3.0</v>
@@ -3318,7 +3321,7 @@
         <v>3.0</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I61" s="3">
         <v>4.0</v>
@@ -3327,7 +3330,7 @@
         <v>3.0</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M61" s="3">
         <v>2.0</v>
@@ -3356,7 +3359,7 @@
         <v>66.0</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E62" s="3">
         <v>3.0</v>
@@ -3365,7 +3368,7 @@
         <v>4.0</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I62" s="3">
         <v>3.0</v>
@@ -3374,7 +3377,7 @@
         <v>1.0</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M62" s="3">
         <v>3.0</v>
@@ -3403,7 +3406,7 @@
         <v>2544.0</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E63" s="3">
         <v>3.0</v>
@@ -3412,7 +3415,7 @@
         <v>3.0</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I63" s="3">
         <v>2.0</v>
@@ -3430,7 +3433,7 @@
         <v>3.0</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q63" s="3">
         <v>4.0</v>
@@ -3450,7 +3453,7 @@
         <v>3881.0</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E64" s="3">
         <v>3.0</v>
@@ -3459,7 +3462,7 @@
         <v>2.0</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I64" s="3">
         <v>4.0</v>
@@ -3468,7 +3471,7 @@
         <v>3.0</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M64" s="3">
         <v>4.0</v>
@@ -3506,7 +3509,7 @@
         <v>3.0</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I65" s="3">
         <v>3.0</v>
@@ -3515,7 +3518,7 @@
         <v>2.0</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M65" s="3">
         <v>4.0</v>
@@ -3524,7 +3527,7 @@
         <v>2.0</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q65" s="3">
         <v>1.0</v>
@@ -3609,7 +3612,7 @@
         <v>46222.172217025465</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C2" s="4">
         <v>3849.0</v>
@@ -3624,7 +3627,7 @@
         <v>4.0</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3">
         <v>2.0</v>
@@ -3633,7 +3636,7 @@
         <v>4.0</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M2" s="3">
         <v>2.0</v>
@@ -3642,7 +3645,7 @@
         <v>4.0</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="3">
         <v>2.0</v>
@@ -3656,7 +3659,7 @@
         <v>46225.60102349537</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" s="4">
         <v>1353.0</v>
@@ -3671,10 +3674,10 @@
         <v>1.0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="3">
         <v>2.0</v>
@@ -3683,10 +3686,10 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M3" s="3">
         <v>1.0</v>
@@ -3695,10 +3698,10 @@
         <v>3.0</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q3" s="3">
         <v>1.0</v>
@@ -3707,7 +3710,7 @@
         <v>3.0</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -3715,13 +3718,13 @@
         <v>46225.624809444445</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4" s="4">
         <v>3382.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3">
         <v>2.0</v>
@@ -3730,7 +3733,7 @@
         <v>3.0</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I4" s="3">
         <v>2.0</v>
@@ -3739,10 +3742,10 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M4" s="3">
         <v>3.0</v>
@@ -3765,13 +3768,13 @@
         <v>46225.62852349537</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4">
         <v>4223.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3">
         <v>2.0</v>
@@ -3780,7 +3783,7 @@
         <v>4.0</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I5" s="3">
         <v>2.0</v>
@@ -3789,10 +3792,10 @@
         <v>3.0</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M5" s="3">
         <v>1.0</v>
@@ -3801,7 +3804,7 @@
         <v>1.0</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>22</v>
@@ -3818,13 +3821,13 @@
         <v>46230.09894773148</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C6" s="4">
         <v>3846.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3">
         <v>3.0</v>
@@ -3833,7 +3836,7 @@
         <v>5.0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I6" s="3">
         <v>1.0</v>
@@ -3842,7 +3845,7 @@
         <v>3.0</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M6" s="3">
         <v>2.0</v>
@@ -3865,13 +3868,13 @@
         <v>46230.10650782408</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4">
         <v>51.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="3">
         <v>1.0</v>
@@ -3880,7 +3883,7 @@
         <v>3.0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I7" s="3">
         <v>2.0</v>
@@ -3889,7 +3892,7 @@
         <v>4.0</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M7" s="3">
         <v>2.0</v>
@@ -3912,13 +3915,13 @@
         <v>46230.113922743054</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C8" s="4">
         <v>1684.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="3">
         <v>3.0</v>
@@ -3927,7 +3930,7 @@
         <v>4.0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I8" s="3">
         <v>2.0</v>
@@ -3945,7 +3948,7 @@
         <v>4.0</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q8" s="3">
         <v>2.0</v>
@@ -3959,13 +3962,13 @@
         <v>46230.123343009254</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C9" s="4">
         <v>2896.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="3">
         <v>2.0</v>
@@ -3974,7 +3977,7 @@
         <v>3.0</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I9" s="3">
         <v>2.0</v>
@@ -3992,7 +3995,7 @@
         <v>3.0</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q9" s="3">
         <v>2.0</v>
@@ -4006,7 +4009,7 @@
         <v>46231.84139128472</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C10" s="4">
         <v>250.0</v>
@@ -4021,7 +4024,7 @@
         <v>4.0</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I10" s="3">
         <v>2.0</v>
@@ -4030,7 +4033,7 @@
         <v>4.0</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M10" s="3">
         <v>2.0</v>
@@ -4039,7 +4042,7 @@
         <v>3.0</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q10" s="3">
         <v>2.0</v>
@@ -4053,13 +4056,13 @@
         <v>46231.84536614583</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C11" s="4">
         <v>2875.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E11" s="3">
         <v>2.0</v>
@@ -4077,7 +4080,7 @@
         <v>4.0</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M11" s="3">
         <v>3.0</v>
@@ -4086,7 +4089,7 @@
         <v>4.0</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q11" s="3">
         <v>3.0</v>
@@ -4100,13 +4103,13 @@
         <v>46232.75054260417</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C12" s="4">
         <v>3325.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E12" s="3">
         <v>1.0</v>
@@ -4124,7 +4127,7 @@
         <v>4.0</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M12" s="3">
         <v>2.0</v>
@@ -4133,7 +4136,7 @@
         <v>5.0</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q12" s="3">
         <v>1.0</v>
@@ -4147,13 +4150,13 @@
         <v>46232.75557686343</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13" s="4">
         <v>1610.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E13" s="3">
         <v>2.0</v>
@@ -4171,7 +4174,7 @@
         <v>3.0</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M13" s="3">
         <v>3.0</v>
@@ -4180,7 +4183,7 @@
         <v>4.0</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q13" s="3">
         <v>2.0</v>
@@ -4194,7 +4197,7 @@
         <v>46232.76180821759</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C14" s="4">
         <v>844.0</v>
@@ -4209,7 +4212,7 @@
         <v>5.0</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I14" s="3">
         <v>1.0</v>
@@ -4218,7 +4221,7 @@
         <v>4.0</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M14" s="3">
         <v>2.0</v>
@@ -4230,7 +4233,7 @@
         <v>32</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q14" s="3">
         <v>4.0</v>
@@ -4244,7 +4247,7 @@
         <v>46232.76564729167</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C15" s="4">
         <v>3013.0</v>
@@ -4259,7 +4262,7 @@
         <v>4.0</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I15" s="3">
         <v>1.0</v>
@@ -4268,7 +4271,7 @@
         <v>4.0</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M15" s="3">
         <v>1.0</v>
@@ -4277,7 +4280,7 @@
         <v>4.0</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q15" s="3">
         <v>1.0</v>
@@ -4291,13 +4294,13 @@
         <v>46232.776407812504</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C16" s="4">
         <v>3159.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E16" s="3">
         <v>1.0</v>
@@ -4318,7 +4321,7 @@
         <v>4.0</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M16" s="3">
         <v>1.0</v>
@@ -4327,7 +4330,7 @@
         <v>4.0</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q16" s="3">
         <v>1.0</v>
@@ -4341,13 +4344,13 @@
         <v>46232.78047136574</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C17" s="4">
         <v>740.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" s="3">
         <v>1.0</v>
@@ -4356,7 +4359,7 @@
         <v>3.0</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I17" s="3">
         <v>1.0</v>
@@ -4374,7 +4377,7 @@
         <v>3.0</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q17" s="3">
         <v>1.0</v>
@@ -4388,7 +4391,7 @@
         <v>46232.78326053241</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C18" s="4">
         <v>3596.0</v>
@@ -4403,7 +4406,7 @@
         <v>5.0</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I18" s="3">
         <v>2.0</v>
@@ -4412,7 +4415,7 @@
         <v>3.0</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M18" s="3">
         <v>1.0</v>
@@ -4421,7 +4424,7 @@
         <v>4.0</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q18" s="3">
         <v>2.0</v>
@@ -4435,13 +4438,13 @@
         <v>46232.78644847222</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C19" s="4">
         <v>2804.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E19" s="3">
         <v>2.0</v>
@@ -4459,7 +4462,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M19" s="3">
         <v>2.0</v>
@@ -4468,7 +4471,7 @@
         <v>3.0</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q19" s="3">
         <v>2.0</v>
@@ -4482,7 +4485,7 @@
         <v>46232.78936142361</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C20" s="4">
         <v>3231.0</v>
@@ -4497,7 +4500,7 @@
         <v>3.0</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I20" s="3">
         <v>2.0</v>
@@ -4506,7 +4509,7 @@
         <v>3.0</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -4518,7 +4521,7 @@
         <v>35</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q20" s="3">
         <v>1.0</v>
@@ -4532,7 +4535,7 @@
         <v>46232.79335375</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C21" s="4">
         <v>121.0</v>
@@ -4547,7 +4550,7 @@
         <v>4.0</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I21" s="3">
         <v>2.0</v>
@@ -4559,7 +4562,7 @@
         <v>36</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M21" s="3">
         <v>1.0</v>
@@ -4571,7 +4574,7 @@
         <v>37</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q21" s="3">
         <v>1.0</v>
@@ -4585,7 +4588,7 @@
         <v>46232.85918023148</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C22" s="4">
         <v>3247.0</v>
@@ -4600,7 +4603,7 @@
         <v>4.0</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I22" s="3">
         <v>2.0</v>
@@ -4609,7 +4612,7 @@
         <v>3.0</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M22" s="3">
         <v>1.0</v>
@@ -4618,7 +4621,7 @@
         <v>4.0</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q22" s="3">
         <v>1.0</v>
@@ -4632,13 +4635,13 @@
         <v>46232.86953215278</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C23" s="4">
         <v>3926.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" s="3">
         <v>2.0</v>
@@ -4647,7 +4650,7 @@
         <v>4.0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I23" s="3">
         <v>3.0</v>
@@ -4665,7 +4668,7 @@
         <v>3.0</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q23" s="3">
         <v>2.0</v>
@@ -4679,13 +4682,13 @@
         <v>46232.87688391204</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C24" s="4">
         <v>1069.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E24" s="3">
         <v>1.0</v>
@@ -4694,7 +4697,7 @@
         <v>2.0</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I24" s="3">
         <v>1.0</v>
@@ -4712,7 +4715,7 @@
         <v>2.0</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q24" s="3">
         <v>1.0</v>
@@ -4726,13 +4729,13 @@
         <v>46232.88261299768</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C25" s="4">
         <v>560.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25" s="3">
         <v>2.0</v>
@@ -4750,7 +4753,7 @@
         <v>5.0</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M25" s="3">
         <v>2.0</v>
@@ -4759,7 +4762,7 @@
         <v>5.0</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q25" s="3">
         <v>2.0</v>
@@ -4773,7 +4776,7 @@
         <v>46233.00159622685</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C26" s="4">
         <v>3056.0</v>
@@ -4788,7 +4791,7 @@
         <v>2.0</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I26" s="3">
         <v>2.0</v>
@@ -4797,7 +4800,7 @@
         <v>3.0</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M26" s="3">
         <v>2.0</v>
@@ -4806,7 +4809,7 @@
         <v>3.0</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q26" s="3">
         <v>2.0</v>
@@ -4820,13 +4823,13 @@
         <v>46233.01361976852</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C27" s="4">
         <v>3341.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E27" s="3">
         <v>1.0</v>
@@ -4835,7 +4838,7 @@
         <v>4.0</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I27" s="3">
         <v>1.0</v>
@@ -4844,7 +4847,7 @@
         <v>4.0</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M27" s="3">
         <v>1.0</v>
@@ -4867,13 +4870,13 @@
         <v>46234.068551226854</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C28" s="4">
         <v>3508.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28" s="3">
         <v>2.0</v>
@@ -4882,7 +4885,7 @@
         <v>4.0</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I28" s="3">
         <v>2.0</v>
@@ -4891,7 +4894,7 @@
         <v>4.0</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M28" s="3">
         <v>1.0</v>
@@ -4914,13 +4917,13 @@
         <v>46234.070875694444</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C29" s="4">
         <v>1952.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E29" s="3">
         <v>4.0</v>
@@ -4938,7 +4941,7 @@
         <v>2.0</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M29" s="3">
         <v>2.0</v>
@@ -4947,7 +4950,7 @@
         <v>4.0</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q29" s="3">
         <v>3.0</v>
@@ -4961,13 +4964,13 @@
         <v>46234.07546523148</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C30" s="4">
         <v>429.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E30" s="3">
         <v>4.0</v>
@@ -4976,7 +4979,7 @@
         <v>4.0</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I30" s="3">
         <v>3.0</v>
@@ -4985,7 +4988,7 @@
         <v>4.0</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M30" s="3">
         <v>3.0</v>
@@ -5008,13 +5011,13 @@
         <v>46234.087179236114</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C31" s="4">
         <v>501.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E31" s="3">
         <v>4.0</v>
@@ -5032,7 +5035,7 @@
         <v>4.0</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M31" s="3">
         <v>3.0</v>
@@ -5041,7 +5044,7 @@
         <v>3.0</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q31" s="3">
         <v>3.0</v>
@@ -5055,7 +5058,7 @@
         <v>46234.0930824074</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C32" s="4">
         <v>1275.0</v>
@@ -5070,7 +5073,7 @@
         <v>3.0</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I32" s="3">
         <v>1.0</v>
@@ -5079,7 +5082,7 @@
         <v>3.0</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M32" s="3">
         <v>1.0</v>
@@ -5091,7 +5094,7 @@
         <v>39</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q32" s="3">
         <v>2.0</v>
@@ -5105,13 +5108,13 @@
         <v>46234.103163645836</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C33" s="4">
         <v>4168.0</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E33" s="3">
         <v>2.0</v>
@@ -5132,7 +5135,7 @@
         <v>3.0</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M33" s="3">
         <v>2.0</v>
@@ -5141,7 +5144,7 @@
         <v>3.0</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q33" s="3">
         <v>2.0</v>
@@ -5155,13 +5158,13 @@
         <v>46238.82448619213</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C34" s="4">
         <v>1482.0</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E34" s="3">
         <v>1.0</v>
@@ -5173,7 +5176,7 @@
         <v>41</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I34" s="3">
         <v>1.0</v>
@@ -5185,7 +5188,7 @@
         <v>41</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M34" s="3">
         <v>3.0</v>
@@ -5214,13 +5217,13 @@
         <v>46238.83467055556</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C35" s="4">
         <v>1876.0</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E35" s="3">
         <v>4.0</v>
@@ -5238,7 +5241,7 @@
         <v>3.0</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M35" s="3">
         <v>3.0</v>
@@ -5250,7 +5253,7 @@
         <v>42</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q35" s="3">
         <v>4.0</v>
@@ -5264,13 +5267,13 @@
         <v>46238.84257037037</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C36" s="4">
         <v>1213.0</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E36" s="3">
         <v>1.0</v>
@@ -5279,7 +5282,7 @@
         <v>4.0</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I36" s="3">
         <v>1.0</v>
@@ -5300,7 +5303,7 @@
         <v>4.0</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q36" s="3">
         <v>1.0</v>
@@ -5314,13 +5317,13 @@
         <v>46238.84952280093</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C37" s="4">
         <v>2016.0</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E37" s="3">
         <v>2.0</v>
@@ -5329,7 +5332,7 @@
         <v>4.0</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I37" s="3">
         <v>1.0</v>
@@ -5350,7 +5353,7 @@
         <v>3.0</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q37" s="3">
         <v>2.0</v>
@@ -5364,13 +5367,13 @@
         <v>46244.98406592592</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C38" s="4">
         <v>3379.0</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" s="3">
         <v>1.0</v>
@@ -5379,7 +5382,7 @@
         <v>3.0</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I38" s="3">
         <v>4.0</v>
@@ -5388,7 +5391,7 @@
         <v>4.0</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M38" s="3">
         <v>1.0</v>
@@ -5411,13 +5414,13 @@
         <v>46244.991957743056</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C39" s="4">
         <v>3397.0</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E39" s="3">
         <v>3.0</v>
@@ -5426,7 +5429,7 @@
         <v>4.0</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I39" s="3">
         <v>3.0</v>
@@ -5435,7 +5438,7 @@
         <v>4.0</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M39" s="3">
         <v>2.0</v>
@@ -5461,13 +5464,13 @@
         <v>46244.999857013885</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C40" s="4">
         <v>1985.0</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E40" s="3">
         <v>2.0</v>
@@ -5476,7 +5479,7 @@
         <v>2.0</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I40" s="3">
         <v>3.0</v>
@@ -5485,7 +5488,7 @@
         <v>3.0</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M40" s="3">
         <v>3.0</v>
@@ -5508,13 +5511,13 @@
         <v>46245.00216123843</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C41" s="4">
         <v>949.0</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E41" s="3">
         <v>2.0</v>
@@ -5523,7 +5526,7 @@
         <v>2.0</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I41" s="3">
         <v>2.0</v>
@@ -5544,7 +5547,7 @@
         <v>4.0</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q41" s="3">
         <v>3.0</v>
@@ -5558,7 +5561,7 @@
         <v>46245.06479855324</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C42" s="4">
         <v>3284.0</v>
@@ -5573,7 +5576,7 @@
         <v>3.0</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I42" s="3">
         <v>3.0</v>
@@ -5582,7 +5585,7 @@
         <v>4.0</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M42" s="3">
         <v>2.0</v>
@@ -5591,7 +5594,7 @@
         <v>3.0</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q42" s="3">
         <v>2.0</v>
@@ -5605,7 +5608,7 @@
         <v>46245.06901409722</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C43" s="4">
         <v>2889.0</v>
@@ -5620,7 +5623,7 @@
         <v>4.0</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I43" s="3">
         <v>3.0</v>
@@ -5629,7 +5632,7 @@
         <v>4.0</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M43" s="3">
         <v>3.0</v>
@@ -5638,7 +5641,7 @@
         <v>4.0</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q43" s="3">
         <v>3.0</v>
@@ -5652,7 +5655,7 @@
         <v>46245.071389386576</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C44" s="4">
         <v>709.0</v>
@@ -5667,7 +5670,7 @@
         <v>1.0</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I44" s="3">
         <v>1.0</v>
@@ -5676,7 +5679,7 @@
         <v>1.0</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M44" s="3">
         <v>4.0</v>
@@ -5685,7 +5688,7 @@
         <v>4.0</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q44" s="3">
         <v>3.0</v>
@@ -5699,13 +5702,13 @@
         <v>46245.076771990745</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C45" s="4">
         <v>3096.0</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E45" s="3">
         <v>3.0</v>
@@ -5714,7 +5717,7 @@
         <v>3.0</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I45" s="3">
         <v>3.0</v>
@@ -5732,7 +5735,7 @@
         <v>4.0</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q45" s="3">
         <v>4.0</v>
@@ -5746,7 +5749,7 @@
         <v>46245.08922303241</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C46" s="4">
         <v>982.0</v>
@@ -5761,7 +5764,7 @@
         <v>4.0</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I46" s="3">
         <v>2.0</v>
@@ -5770,7 +5773,7 @@
         <v>3.0</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M46" s="3">
         <v>2.0</v>
@@ -5779,7 +5782,7 @@
         <v>2.0</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Q46" s="3">
         <v>2.0</v>
@@ -5793,7 +5796,7 @@
         <v>46245.094949074075</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C47" s="4">
         <v>3344.0</v>
@@ -5808,7 +5811,7 @@
         <v>3.0</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I47" s="3">
         <v>3.0</v>
@@ -5820,7 +5823,7 @@
         <v>45</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M47" s="3">
         <v>3.0</v>
@@ -5829,7 +5832,7 @@
         <v>2.0</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q47" s="3">
         <v>2.0</v>
@@ -5843,13 +5846,13 @@
         <v>46245.09878515046</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C48" s="4">
         <v>1375.0</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E48" s="3">
         <v>3.0</v>
@@ -5867,7 +5870,7 @@
         <v>3.0</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M48" s="3">
         <v>3.0</v>
@@ -5876,7 +5879,7 @@
         <v>3.0</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q48" s="3">
         <v>3.0</v>
@@ -5890,7 +5893,7 @@
         <v>46245.10444263888</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C49" s="4">
         <v>993.0</v>
@@ -5905,7 +5908,7 @@
         <v>5.0</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I49" s="3">
         <v>2.0</v>
@@ -5914,7 +5917,7 @@
         <v>5.0</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M49" s="3">
         <v>4.0</v>
@@ -5923,13 +5926,780 @@
         <v>5.0</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q49" s="3">
         <v>4.0</v>
       </c>
       <c r="R49" s="3">
         <v>5.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>46246.09928751158</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="4">
+        <v>3812.0</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F50" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J50" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M50" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>46246.10415792824</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1614.0</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F51" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J51" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M51" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>46246.10643712963</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="4">
+        <v>855.0</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M52" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N52" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>46246.110177083334</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="4">
+        <v>4234.0</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F53" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J53" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>46246.68995649306</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="4">
+        <v>3286.0</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F54" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M54" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N54" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R54" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>46246.69855392361</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="4">
+        <v>3652.0</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F55" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J55" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M55" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N55" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R55" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>46246.70038637731</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="4">
+        <v>3824.0</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F56" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M56" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="N56" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R56" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>46246.70582190972</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="4">
+        <v>2911.0</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F57" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M57" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N57" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R57" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>46247.10651681713</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="4">
+        <v>2062.0</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M58" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>46247.11941072917</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="4">
+        <v>3143.0</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M59" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N59" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R59" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>46247.12811152778</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="4">
+        <v>4075.0</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J60" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N60" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R60" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>46247.13212930555</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="4">
+        <v>66.0</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M61" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <v>46247.67846491898</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="4">
+        <v>2544.0</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M62" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N62" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R62" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <v>46247.747536180555</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="4">
+        <v>3881.0</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="J63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <v>46247.751237627315</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="4">
+        <v>986.0</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F64" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J64" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M64" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>46247.75870796296</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="4">
+        <v>945.0</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F65" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M65" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>
